--- a/docs/review/packs/chapter-3.11.xlsx
+++ b/docs/review/packs/chapter-3.11.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>10,546</t>
+          <t>10,687</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14">
@@ -924,7 +924,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1005</v>
+        <v>1146</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Treat the Kaplan fibres as the structure that makes the tenodesis a reconstruction rather than an improvisation.</t>
+          <t>Read their consistency in dissection as the point distinguishing them from the anterolateral ligament.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Treat the complex rather than a single structure as the target.</t>
+          <t>Treat the Kaplan fibres as the structure that makes the tenodesis a reconstruction rather than an improvisation.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Expect no measurement to confirm which structure a construct reproduces.</t>
+          <t>Treat the complex rather than a single structure as the target.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -2043,12 +2043,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Plan distal lateral femoral fixation positions together when several are needed.</t>
+          <t>Expect no measurement to confirm which structure a construct reproduces.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -2058,22 +2058,22 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3.11.3-P1</t>
+          <t>3.11.2-P6</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>3.11.3</t>
+          <t>3.11.2</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Use the complex as the term and the region as the unit when discussing function.</t>
+          <t>Plan distal lateral femoral fixation positions together when several are needed.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2083,22 +2083,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.11.3-P2</t>
+          <t>3.11.2-P7</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3.11.3</t>
+          <t>3.11.2</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Expect prevalence figures to vary between dissection studies.</t>
+          <t>Accept that the optimal point within the region is not established.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2108,7 +2108,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.11.3-P3</t>
+          <t>3.11.3-P1</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Treat its contribution as clinically relevant in combination with cruciate injury.</t>
+          <t>Use the complex as the term and the region as the unit when discussing function.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2133,7 +2133,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.11.3-P4</t>
+          <t>3.11.3-P2</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Treat the structure as real enough to reconstruct and disputed enough that the reconstruction's rationale should be stated regionally rather than anatomically.</t>
+          <t>Expect prevalence figures to vary between dissection studies.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.11.3-P5</t>
+          <t>3.11.3-P3</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Prefer a tenodesis where tibial tunnel crowding is a constraint.</t>
+          <t>Treat its contribution as clinically relevant in combination with cruciate injury.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.11.3-P6</t>
+          <t>3.11.3-P4</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Plan femoral fixation positions together when several are needed.</t>
+          <t>Treat the structure as real enough to reconstruct and disputed enough that the reconstruction's rationale should be stated regionally rather than anatomically.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2208,22 +2208,22 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.11.4-P1</t>
+          <t>3.11.3-P5</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>3.11.4</t>
+          <t>3.11.3</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Consider lateral meniscal injury as well as anterolateral injury in a high grade.</t>
+          <t>State the rationale regionally rather than anatomically when discussing the structure.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2233,22 +2233,22 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.11.4-P2</t>
+          <t>3.11.3-P6</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>3.11.4</t>
+          <t>3.11.3</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Measure slope where the grade exceeds what the injury explains.</t>
+          <t>Prefer a tenodesis where tibial tunnel crowding is a constraint.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2258,22 +2258,22 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.11.4-P3</t>
+          <t>3.11.3-P7</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>3.11.4</t>
+          <t>3.11.3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Treat pivot shift control as the outcome a lateral procedure is added to achieve, and the grade as the indication.</t>
+          <t>Plan femoral fixation positions together when several are needed.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -2283,22 +2283,22 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.11.4-P4</t>
+          <t>3.11.3-P8</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3.11.4</t>
+          <t>3.11.3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Check the pivot shift under anaesthetic after cruciate fixation.</t>
+          <t>Accept that no measurement matches construct to knee.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2308,7 +2308,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.11.4-P5</t>
+          <t>3.11.4-P1</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Repair the lateral posterior horn, which also controls the subluxation.</t>
+          <t>Read a high grade as narrowing the possibilities rather than naming a structure.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -2333,7 +2333,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.11.4-P6</t>
+          <t>3.11.4-P2</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Measure slope in a high grade shift, particularly before revision.</t>
+          <t>Consider lateral meniscal injury as well as anterolateral injury in a high grade.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2358,12 +2358,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.11.5-P1</t>
+          <t>3.11.4-P3</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3.11.5</t>
+          <t>3.11.4</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Repair the lateral posterior horn, which has a rotational rationale.</t>
+          <t>Measure slope where the grade exceeds what the injury explains.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2383,12 +2383,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.11.5-P2</t>
+          <t>3.11.4-P4</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>3.11.5</t>
+          <t>3.11.4</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Measure slope where rotation exceeds what the injury explains.</t>
+          <t>Grade under anaesthetic where the grade will change the operation.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2408,12 +2408,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.11.5-P3</t>
+          <t>3.11.4-P5</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>3.11.5</t>
+          <t>3.11.4</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Treat internal rotation control as the quantity the whole anterolateral debate is about, and over-constraint as the cost that makes the debate a real one.</t>
+          <t>Treat pivot shift control as the outcome a lateral procedure is added to achieve, and the grade as the indication.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2433,12 +2433,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.11.5-P4</t>
+          <t>3.11.4-P6</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>3.11.5</t>
+          <t>3.11.4</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Expect cadaveric over-constraint risk not to have appeared as clinical stiffness in trials.</t>
+          <t>Check the pivot shift under anaesthetic after cruciate fixation.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2458,12 +2458,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.11.5-P5</t>
+          <t>3.11.4-P7</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>3.11.5</t>
+          <t>3.11.4</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Plan the two constructs' tunnels together, since they interact.</t>
+          <t>Add a lateral procedure where the grade or the population indicates it.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -2483,22 +2483,22 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.11.6-P1</t>
+          <t>3.11.4-P8</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3.11.6</t>
+          <t>3.11.4</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Seeing it on a plain radiograph should prompt a search for a cruciate injury rather than treatment of the fragment.</t>
+          <t>Repair the lateral posterior horn, which also controls the subluxation.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2508,22 +2508,22 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.11.6-P2</t>
+          <t>3.11.4-P9</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>3.11.6</t>
+          <t>3.11.4</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Expect a higher grade pivot shift where it is present.</t>
+          <t>Measure slope in a high grade shift, particularly before revision.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -2533,12 +2533,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.11.6-P3</t>
+          <t>3.11.5-P1</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>3.11.6</t>
+          <t>3.11.5</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Use it as evidence of an attachment region rather than of a named structure.</t>
+          <t>Repair the lateral posterior horn, which has a rotational rationale.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -2558,22 +2558,22 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.11.6-P4</t>
+          <t>3.11.5-P2</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>3.11.6</t>
+          <t>3.11.5</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Treat the lesion as an indication to consider a lateral procedure, on the ground that it is direct evidence of anterolateral injury in a knee where that is otherwise inferred.</t>
+          <t>Measure slope where rotation exceeds what the injury explains.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -2583,12 +2583,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.11.6-P5</t>
+          <t>3.11.5-P3</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3.11.6</t>
+          <t>3.11.5</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Consider a lateral procedure where the lesion is present.</t>
+          <t>Treat internal rotation control as the quantity the whole anterolateral debate is about, and over-constraint as the cost that makes the debate a real one.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -2608,12 +2608,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.11.6-P6</t>
+          <t>3.11.5-P4</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>3.11.6</t>
+          <t>3.11.5</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Leave the fragment unfixed unless it is large and displaced.</t>
+          <t>Expect cadaveric over-constraint risk not to have appeared as clinical stiffness in trials.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2633,12 +2633,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.11.7-P1</t>
+          <t>3.11.5-P5</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3.11.7</t>
+          <t>3.11.5</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Treat the tenodesis as the augmentation with the strongest clinical evidence and the weakest anatomical rationale, and treat that combination as acceptable.</t>
+          <t>Plan the two constructs' tunnels together, since they interact.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -2658,22 +2658,22 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.11.7-P2</t>
+          <t>3.11.6-P1</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>3.11.7</t>
+          <t>3.11.6</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Plan it alongside the cruciate graft rather than as an afterthought.</t>
+          <t>Seeing it on a plain radiograph should prompt a search for a cruciate injury rather than treatment of the fragment.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2683,22 +2683,22 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.11.7-P3</t>
+          <t>3.11.6-P2</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3.11.7</t>
+          <t>3.11.6</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Plan femoral fixation alongside the cruciate tunnel.</t>
+          <t>Read it as indicating anterolateral and cruciate injury rather than as a fracture to treat.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2708,22 +2708,22 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.11.7-P4</t>
+          <t>3.11.6-P3</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>3.11.7</t>
+          <t>3.11.6</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Consider slope correction as an alternative or an addition in the right knee.</t>
+          <t>Expect a higher grade pivot shift where it is present.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2733,12 +2733,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.11.8-P1</t>
+          <t>3.11.6-P4</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3.11.8</t>
+          <t>3.11.6</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Order of fixation and the rotational position at each.</t>
+          <t>Use it as evidence of an attachment region rather than of a named structure.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -2758,22 +2758,22 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.11.8-P2</t>
+          <t>3.11.6-P5</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>3.11.8</t>
+          <t>3.11.6</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Plan both femoral fixations together to avoid convergence.</t>
+          <t>Treat the lesion as an indication to consider a lateral procedure, on the ground that it is direct evidence of anterolateral injury in a knee where that is otherwise inferred.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2783,22 +2783,22 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.11.8-P3</t>
+          <t>3.11.6-P6</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>3.11.8</t>
+          <t>3.11.6</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Expect the load sharing to be demonstrable in cadavers and not in a patient.</t>
+          <t>Consider a lateral procedure where the lesion is present.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2808,12 +2808,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.11.8-P4</t>
+          <t>3.11.6-P7</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>3.11.8</t>
+          <t>3.11.6</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Treat the combination as the current answer for the high risk knee and the indications as the part still being refined.</t>
+          <t>Leave the fragment unfixed unless it is large and displaced.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2833,12 +2833,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.11.8-P5</t>
+          <t>3.11.6-P8</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>3.11.8</t>
+          <t>3.11.6</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Consider slope correction as an alternative in the right knee.</t>
+          <t>Grade the pivot shift under anaesthetic, which the lesion predicts will be higher.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2858,12 +2858,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.11.8-P6</t>
+          <t>3.11.7-P1</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>3.11.8</t>
+          <t>3.11.7</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Plan graft and fixation space for both constructs before theatre.</t>
+          <t>Treat the tenodesis as the augmentation with the strongest clinical evidence and the weakest anatomical rationale, and treat that combination as acceptable.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2883,22 +2883,22 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.11.8-P7</t>
+          <t>3.11.7-P2</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3.11.8</t>
+          <t>3.11.7</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Plan tunnel geometry and slope correction together in a revision.</t>
+          <t>Add it in the groups the trial evidence covers rather than universally.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -2908,22 +2908,22 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.11.8-P8</t>
+          <t>3.11.7-P3</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>3.11.8</t>
+          <t>3.11.7</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Prefer a tenodesis, which adds no tibial tunnel.</t>
+          <t>State that the stiffness objection has not been borne out at current tensions.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -2933,12 +2933,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P1</t>
+          <t>3.11.7-P4</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>3.11.9</t>
+          <t>3.11.7</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Avoid citing a dissection study to settle a clinical question.</t>
+          <t>Plan it alongside the cruciate graft rather than as an afterthought.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -2958,12 +2958,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P2</t>
+          <t>3.11.7-P5</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>3.11.9</t>
+          <t>3.11.7</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Measure slope before choosing between augmentation and correction.</t>
+          <t>Plan femoral fixation alongside the cruciate tunnel.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2983,12 +2983,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P3</t>
+          <t>3.11.7-P6</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>3.11.9</t>
+          <t>3.11.7</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Consider both in the knee that has failed a conventional revision.</t>
+          <t>Consider slope correction as an alternative or an addition in the right knee.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -3008,22 +3008,22 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P4</t>
+          <t>3.11.7-P7</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>3.11.9</t>
+          <t>3.11.7</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>consultant</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Follow registry and subgroup data as it accumulates.</t>
+          <t>State that no measurement identifies the individual who needs one.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -3033,22 +3033,22 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P5</t>
+          <t>3.11.8-P1</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>3.11.9</t>
+          <t>3.11.8</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>consultant</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Do not cite the anatomical dispute as a reason against augmentation.</t>
+          <t>Order of fixation and the rotational position at each.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -3058,31 +3058,481 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P6</t>
+          <t>3.11.8-P2</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>3.11.9</t>
+          <t>3.11.8</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>consultant</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Expect slope correction to continue competing for the same indication.</t>
+          <t>Plan both femoral fixations together to avoid convergence.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="inlineStr"/>
     </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8-P3</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Expect the load sharing to be demonstrable in cadavers and not in a patient.</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8-P4</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Treat the combination as the current answer for the high risk knee and the indications as the part still being refined.</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8-P5</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Add a lateral procedure in the high risk groups the trials cover.</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8-P6</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Consider slope correction as an alternative in the right knee.</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8-P7</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Plan graft and fixation space for both constructs before theatre.</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8-P8</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>State that routine against selective use is unsettled.</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8-P9</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Plan tunnel geometry and slope correction together in a revision.</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8-P10</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Prefer a tenodesis, which adds no tibial tunnel.</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8-P11</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>3.11.8</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Stage where tunnels, graft or soft tissues will not allow one sitting.</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9-P1</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Avoid citing a dissection study to settle a clinical question.</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9-P2</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Measure slope before choosing between augmentation and correction.</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9-P3</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Consider both in the knee that has failed a conventional revision.</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9-P4</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>State that no trial compares them directly.</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9-P5</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Set the question out as a balance and name what sits on each side of it.</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9-P6</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Weigh age and pivoting demand first, because the benefit concentrates there.</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9-P7</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Measure slope before treating augmentation as the only available lever.</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9-P8</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Price a second failure into the revision decision rather than into the primary one.</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9-P9</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Accept that the same evidence can be weighed differently without either consultant being wrong.</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3263,7 +3713,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>50</f>
+        <f>68</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -3278,7 +3728,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E52,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E70,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -3308,7 +3758,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E52,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E70,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -3320,7 +3770,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E52,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E70,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -3332,7 +3782,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E52,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E70,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -3344,7 +3794,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E52,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E70,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>

--- a/docs/review/packs/chapter-3.11.xlsx
+++ b/docs/review/packs/chapter-3.11.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>10,687</t>
+          <t>10,869</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -924,7 +924,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1146</v>
+        <v>1328</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3308,22 +3308,22 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P1</t>
+          <t>3.11.8-P12</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>3.11.9</t>
+          <t>3.11.8</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Avoid citing a dissection study to settle a clinical question.</t>
+          <t>Counsel that revision outcomes are worse than primary.</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P2</t>
+          <t>3.11.9-P1</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Measure slope before choosing between augmentation and correction.</t>
+          <t>Avoid citing a dissection study to settle a clinical question.</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -3358,7 +3358,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P3</t>
+          <t>3.11.9-P2</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Consider both in the knee that has failed a conventional revision.</t>
+          <t>Measure slope before choosing between augmentation and correction.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3383,7 +3383,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P4</t>
+          <t>3.11.9-P3</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>State that no trial compares them directly.</t>
+          <t>Consider both in the knee that has failed a conventional revision.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -3408,7 +3408,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P5</t>
+          <t>3.11.9-P4</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>consultant</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Set the question out as a balance and name what sits on each side of it.</t>
+          <t>State that no trial compares them directly.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -3433,7 +3433,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P6</t>
+          <t>3.11.9-P5</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Weigh age and pivoting demand first, because the benefit concentrates there.</t>
+          <t>Set the question out as a balance and name what sits on each side of it.</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr"/>
@@ -3458,7 +3458,7 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P7</t>
+          <t>3.11.9-P6</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Measure slope before treating augmentation as the only available lever.</t>
+          <t>Weigh age and pivoting demand first, because the benefit concentrates there.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -3483,7 +3483,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P8</t>
+          <t>3.11.9-P7</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Price a second failure into the revision decision rather than into the primary one.</t>
+          <t>Measure slope before treating augmentation as the only available lever.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
@@ -3508,7 +3508,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>3.11.9-P9</t>
+          <t>3.11.9-P8</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -3523,16 +3523,66 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Accept that the same evidence can be weighed differently without either consultant being wrong.</t>
+          <t>Price a second failure into the revision decision rather than into the primary one.</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9-P9</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Take age and physiology, comorbidities, knee demand, psychological state and the patient's own ideas, concerns and expectations into the decision explicitly, because a trial population carries none of them.</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9-P10</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>3.11.9</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Accept that the same evidence can be weighed differently without either consultant being wrong.</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3713,7 +3763,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>68</f>
+        <f>70</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -3728,7 +3778,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E70,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E72,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -3758,7 +3808,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E70,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E72,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -3770,7 +3820,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E70,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E72,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -3782,7 +3832,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E70,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E72,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -3794,7 +3844,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E70,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E72,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
